--- a/Схема бд.xlsx
+++ b/Схема бд.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Python\BernensAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C0045D3-A231-46EA-83B9-B2965730EF5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9491932F-5599-4808-B878-8262E9B2DBA8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3456" yWindow="3456" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
+    <workbookView xWindow="7656" yWindow="3720" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -230,13 +231,37 @@
   </si>
   <si>
     <t>Контакты (переделать)</t>
+  </si>
+  <si>
+    <t>Итоговая карта (коротко и чётко — как в курсовую можно вставлять)</t>
+  </si>
+  <si>
+    <t>cars</t>
+  </si>
+  <si>
+    <t>Автомобили, Мототехника, Фото_авто, Фото_мототехники, Избранное</t>
+  </si>
+  <si>
+    <t>accounts</t>
+  </si>
+  <si>
+    <t>evaluations</t>
+  </si>
+  <si>
+    <t>services</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>Новости, Контакты</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,13 +279,28 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -290,19 +330,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -313,6 +347,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -642,514 +690,514 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="7"/>
+      <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="E5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="D19" s="3" t="s">
+      <c r="B19" s="10"/>
+      <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="E20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="G27" s="3" t="s">
+      <c r="B27" s="6"/>
+      <c r="G27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="B29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="B30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1169,4 +1217,69 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B7477F6-9EF0-4781-B7E7-F56E8973BE88}">
+  <dimension ref="A3:A18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="1:1" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Схема бд.xlsx
+++ b/Схема бд.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Python\BernensAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9491932F-5599-4808-B878-8262E9B2DBA8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6577478-BC49-4DA9-96B5-6BCE8A62664B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7656" yWindow="3720" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
+    <workbookView xWindow="0" yWindow="204" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -347,20 +347,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -690,18 +688,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="10"/>
+      <c r="D2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -777,7 +775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -790,10 +788,10 @@
       <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -882,10 +880,10 @@
       <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="6"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -962,10 +960,10 @@
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D18" s="2" t="s">
@@ -974,16 +972,16 @@
       <c r="E18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="10"/>
+      <c r="B19" s="9"/>
       <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1104,10 +1102,10 @@
       <c r="E25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="6"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
@@ -1124,10 +1122,10 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="6"/>
+      <c r="B27" s="9"/>
       <c r="G27" s="2" t="s">
         <v>59</v>
       </c>
@@ -1225,32 +1223,32 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="1:1" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="11" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1260,17 +1258,17 @@
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="11" t="s">
         <v>72</v>
       </c>
     </row>

--- a/Схема бд.xlsx
+++ b/Схема бд.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Python\BernensAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6577478-BC49-4DA9-96B5-6BCE8A62664B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0040133C-39D9-4792-B696-E66FEABDDC46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="204" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
+    <workbookView xWindow="0" yWindow="204" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -255,6 +257,90 @@
   </si>
   <si>
     <t>Новости, Контакты</t>
+  </si>
+  <si>
+    <t>#F1F1F2</t>
+  </si>
+  <si>
+    <t>#BCBABE</t>
+  </si>
+  <si>
+    <t>#A1D6E2</t>
+  </si>
+  <si>
+    <t>#1995AD</t>
+  </si>
+  <si>
+    <t>Просмотр своих заявок на оценку/комисионную продажу</t>
+  </si>
+  <si>
+    <t>Добавление авто в избранное</t>
+  </si>
+  <si>
+    <t>Личный кабинет</t>
+  </si>
+  <si>
+    <t>Контакты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ </t>
+  </si>
+  <si>
+    <t>Просмотр новостей</t>
+  </si>
+  <si>
+    <t>Просмотр данных доп услуг (автомойка, полировка и т.д.)</t>
+  </si>
+  <si>
+    <t>Раздел мототехника</t>
+  </si>
+  <si>
+    <t>Обмен трейд ин</t>
+  </si>
+  <si>
+    <t>отправка запроса на приблизительную оценку</t>
+  </si>
+  <si>
+    <t>отправить авто на оценку</t>
+  </si>
+  <si>
+    <t>запись на срочную оценку в ирл</t>
+  </si>
+  <si>
+    <t>записаться</t>
+  </si>
+  <si>
+    <t>Срочный выкуп автомобиля</t>
+  </si>
+  <si>
+    <t>Комисионная продажа (Пользователь оставляет заявку на сайте о продаже своего авто с помощью автосалона, заявка уходит на одобрение менеджера/админа)</t>
+  </si>
+  <si>
+    <t>Просмотр цен в эквиваленте к доллару</t>
+  </si>
+  <si>
+    <t>Просматривать данные об продаваемых авто (фильтрация данных) (В случае комиссионной продажи плашка "по предварительной записи")</t>
+  </si>
+  <si>
+    <t>Пользователь</t>
+  </si>
+  <si>
+    <t>Третье лицо (менеджер) может просматривать отправленные запросы на оценку машины и давать приблизительную оценку</t>
+  </si>
+  <si>
+    <t>Администратору полное ведение базы данных</t>
+  </si>
+  <si>
+    <t>Доп услуги</t>
+  </si>
+  <si>
+    <t>Марка</t>
+  </si>
+  <si>
+    <t>Тип кузова</t>
+  </si>
+  <si>
+    <t>БД таблицы</t>
   </si>
 </sst>
 </file>
@@ -352,13 +438,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -374,6 +460,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>319667</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>72244</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1C2C521-D505-4716-BEB9-6ABF55DEE1D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2148467" cy="2440020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -688,18 +823,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="G2" s="9" t="s">
+      <c r="E2" s="10"/>
+      <c r="G2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="9"/>
+      <c r="H2" s="10"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -788,10 +923,10 @@
       <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -880,10 +1015,10 @@
       <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -960,10 +1095,10 @@
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D18" s="2" t="s">
@@ -972,16 +1107,16 @@
       <c r="E18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="9"/>
+      <c r="B19" s="10"/>
       <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1102,10 +1237,10 @@
       <c r="E25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="9"/>
+      <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
@@ -1122,10 +1257,10 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="9"/>
+      <c r="B27" s="10"/>
       <c r="G27" s="2" t="s">
         <v>59</v>
       </c>
@@ -1248,7 +1383,7 @@
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1268,13 +1403,173 @@
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED25FB6-47D7-4232-AFCC-43B927596EE0}">
+  <dimension ref="E4:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2B9AA0-2269-406F-94D2-FD24E1E3AE0E}">
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Схема бд.xlsx
+++ b/Схема бд.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Python\BernensAuto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0040133C-39D9-4792-B696-E66FEABDDC46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7065BEB-754D-43AC-BB08-2D5C17EF2CF5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="204" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
+    <workbookView xWindow="0" yWindow="204" windowWidth="23040" windowHeight="12204" xr2:uid="{59A2B922-0A9C-4FB4-AAF4-EF3A1032F1ED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="схема бд(первонач)" sheetId="1" r:id="rId1"/>
+    <sheet name="приложения" sheetId="2" r:id="rId2"/>
+    <sheet name="гамма" sheetId="3" r:id="rId3"/>
     <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
